--- a/Choke_Slam_export.xlsx
+++ b/Choke_Slam_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1252"/>
+  <dimension ref="A1:Q1267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85120,6 +85120,1038 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>The Miz vs. SANADA vs. Satoshi Kojima</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr"/>
+      <c r="G1253" t="inlineStr"/>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>The Miz, SANADA, Satoshi Kojima</t>
+        </is>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>SANADA</t>
+        </is>
+      </c>
+      <c r="J1253" t="inlineStr">
+        <is>
+          <t>The Miz, Satoshi Kojima</t>
+        </is>
+      </c>
+      <c r="K1253" t="inlineStr"/>
+      <c r="L1253" t="inlineStr">
+        <is>
+          <t>SANADA won a triple threat match against The Miz &amp; Satoshi Kojima in  22:06</t>
+        </is>
+      </c>
+      <c r="M1253" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="N1253" t="n">
+        <v>104</v>
+      </c>
+      <c r="O1253" t="inlineStr">
+        <is>
+          <t>★★★★★¼</t>
+        </is>
+      </c>
+      <c r="P1253" t="inlineStr"/>
+      <c r="Q1253" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Beat the Clock: Masahiro Chono vs. Will Ospreay</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>Beat the Clock</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr"/>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>Masahiro Chono, Will Ospreay</t>
+        </is>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>Will Ospreay</t>
+        </is>
+      </c>
+      <c r="J1254" t="inlineStr">
+        <is>
+          <t>Masahiro Chono</t>
+        </is>
+      </c>
+      <c r="K1254" t="inlineStr"/>
+      <c r="L1254" t="inlineStr">
+        <is>
+          <t>Will Ospreay beat Masahiro Chono in 22 Min 0 Sec with a High Angle Tiger Driver</t>
+        </is>
+      </c>
+      <c r="M1254" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="N1254" t="n">
+        <v>92</v>
+      </c>
+      <c r="O1254" t="inlineStr">
+        <is>
+          <t>★★★★½</t>
+        </is>
+      </c>
+      <c r="P1254" t="inlineStr"/>
+      <c r="Q1254" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Beat the Clock: Steve Austin vs. Will Ospreay</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>Beat the Clock</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr"/>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>Steve Austin, Will Ospreay</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>Will Ospreay</t>
+        </is>
+      </c>
+      <c r="J1255" t="inlineStr">
+        <is>
+          <t>Steve Austin</t>
+        </is>
+      </c>
+      <c r="K1255" t="inlineStr"/>
+      <c r="L1255" t="inlineStr">
+        <is>
+          <t>Will Ospreay beat Steve Austin in 18 Min 26 Sec with a Hidden Blade</t>
+        </is>
+      </c>
+      <c r="M1255" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="N1255" t="n">
+        <v>91</v>
+      </c>
+      <c r="O1255" t="inlineStr">
+        <is>
+          <t>★★★★¼</t>
+        </is>
+      </c>
+      <c r="P1255" t="inlineStr"/>
+      <c r="Q1255" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Beat the Clock: Yokozuna vs. Will Ospreay</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Beat the Clock</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr"/>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>Yokozuna, Will Ospreay</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>Will Ospreay</t>
+        </is>
+      </c>
+      <c r="J1256" t="inlineStr">
+        <is>
+          <t>Yokozuna</t>
+        </is>
+      </c>
+      <c r="K1256" t="inlineStr"/>
+      <c r="L1256" t="inlineStr">
+        <is>
+          <t>Will Ospreay beat Yokozuna in 16 Min 39 Sec with a Hidden Blade</t>
+        </is>
+      </c>
+      <c r="M1256" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="N1256" t="n">
+        <v>83</v>
+      </c>
+      <c r="O1256" t="inlineStr">
+        <is>
+          <t>★★★¾</t>
+        </is>
+      </c>
+      <c r="P1256" t="inlineStr"/>
+      <c r="Q1256" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Madusa vs. Megumi Kudo vs. Rosemary</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr"/>
+      <c r="G1257" t="inlineStr"/>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>Madusa, Megumi Kudo, Rosemary</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>Megumi Kudo</t>
+        </is>
+      </c>
+      <c r="J1257" t="inlineStr">
+        <is>
+          <t>Madusa, Rosemary</t>
+        </is>
+      </c>
+      <c r="K1257" t="inlineStr"/>
+      <c r="L1257" t="inlineStr">
+        <is>
+          <t>Megumi Kudo won a triple threat match against Madusa &amp; Rosemary in  29:28</t>
+        </is>
+      </c>
+      <c r="M1257" t="inlineStr">
+        <is>
+          <t>29:28</t>
+        </is>
+      </c>
+      <c r="N1257" t="n">
+        <v>99</v>
+      </c>
+      <c r="O1257" t="inlineStr">
+        <is>
+          <t>★★★★¾</t>
+        </is>
+      </c>
+      <c r="P1257" t="inlineStr"/>
+      <c r="Q1257" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>Choke Slam Womens Championship: Megumi Kudo vs. Sasha Banks (c)</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr"/>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>Choke Slam Womens Championship</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>Megumi Kudo, Sasha Banks</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>Sasha Banks</t>
+        </is>
+      </c>
+      <c r="J1258" t="inlineStr">
+        <is>
+          <t>Megumi Kudo</t>
+        </is>
+      </c>
+      <c r="K1258" t="inlineStr"/>
+      <c r="L1258" t="inlineStr">
+        <is>
+          <t>Sasha Banks beat Megumi Kudo in 13 Min 26 Sec with a Frog Splash</t>
+        </is>
+      </c>
+      <c r="M1258" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="N1258" t="n">
+        <v>81</v>
+      </c>
+      <c r="O1258" t="inlineStr">
+        <is>
+          <t>★★★¾</t>
+        </is>
+      </c>
+      <c r="P1258" t="inlineStr"/>
+      <c r="Q1258" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>Choke Slam Tag Team Championship - Gauntlet Rumble</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Tag Team</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr"/>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>Mick Foley, Matt Jackson, Cesaro, Chris Benoit, Randy Orton, Matanza Cueto, Nick Jackson, Kazuchika Okada, Zack Sabre Jr., Bam Bam Bigelow</t>
+        </is>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>Nick Jackson</t>
+        </is>
+      </c>
+      <c r="J1259" t="inlineStr"/>
+      <c r="K1259" t="inlineStr"/>
+      <c r="L1259" t="inlineStr">
+        <is>
+          <t>Nick Jackson won a 10 wrestler Royal Rumble in  44:33</t>
+        </is>
+      </c>
+      <c r="M1259" t="inlineStr">
+        <is>
+          <t>44:33</t>
+        </is>
+      </c>
+      <c r="N1259" t="n">
+        <v>100</v>
+      </c>
+      <c r="O1259" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="P1259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Most Eliminations: Zack Sabre Jr. (4)
+Longest Time in Rumble: Kazuchika Okada (42:29)
+Shortest Time in Rumble:Matt Jackson (16:41)</t>
+        </is>
+      </c>
+      <c r="Q1259" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>Stadium Stampede: Militanter Mummenschanz vs. Pentagon &amp; Rey Fenix &amp; Pac</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr"/>
+      <c r="G1260" t="inlineStr"/>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>Mick Foley, Rosemary, SANADA, Penta, Rey Fenix, Pac</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>Mick Foley, Rosemary, SANADA</t>
+        </is>
+      </c>
+      <c r="J1260" t="inlineStr">
+        <is>
+          <t>Penta, Rey Fenix, Pac</t>
+        </is>
+      </c>
+      <c r="K1260" t="inlineStr"/>
+      <c r="L1260" t="inlineStr">
+        <is>
+          <t>Rosemary beat Rey Fenix in 2 Min 34 Sec with a K.O</t>
+        </is>
+      </c>
+      <c r="M1260" t="inlineStr">
+        <is>
+          <t>2:34</t>
+        </is>
+      </c>
+      <c r="N1260" t="n">
+        <v>50</v>
+      </c>
+      <c r="O1260" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="P1260" t="inlineStr"/>
+      <c r="Q1260" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>Stadium Stampede: Sweet 'n Sour Elite vs. Pentagon &amp; Rey Fenix &amp; Pac</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr"/>
+      <c r="G1261" t="inlineStr"/>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>Cesaro, Matanza Cueto, Satoshi Kojima, Penta, Rey Fenix, Pac</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>Cesaro, Matanza Cueto, Satoshi Kojima</t>
+        </is>
+      </c>
+      <c r="J1261" t="inlineStr">
+        <is>
+          <t>Penta, Rey Fenix, Pac</t>
+        </is>
+      </c>
+      <c r="K1261" t="inlineStr"/>
+      <c r="L1261" t="inlineStr">
+        <is>
+          <t>Matanza Cueto beat Penta   in 12 Min 15 Sec with a Wrath of the Gods</t>
+        </is>
+      </c>
+      <c r="M1261" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="N1261" t="n">
+        <v>74</v>
+      </c>
+      <c r="O1261" t="inlineStr">
+        <is>
+          <t>★★★¼</t>
+        </is>
+      </c>
+      <c r="P1261" t="inlineStr"/>
+      <c r="Q1261" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>Stadium Stampede: Saint Rebel Radicalz vs. Penta &amp; Pac &amp; Rey Fenix</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr"/>
+      <c r="G1262" t="inlineStr"/>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>Chris Benoit, The Miz, Yokozuna, Pac, Penta, Rey Fenix</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>Pac, Penta, Rey Fenix</t>
+        </is>
+      </c>
+      <c r="J1262" t="inlineStr">
+        <is>
+          <t>Chris Benoit, The Miz, Yokozuna</t>
+        </is>
+      </c>
+      <c r="K1262" t="inlineStr"/>
+      <c r="L1262" t="inlineStr">
+        <is>
+          <t>Penta   beat Chris Benoit in 16 Min 17 Sec with a Reverse Slingblade</t>
+        </is>
+      </c>
+      <c r="M1262" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="N1262" t="n">
+        <v>82</v>
+      </c>
+      <c r="O1262" t="inlineStr">
+        <is>
+          <t>★★★¾</t>
+        </is>
+      </c>
+      <c r="P1262" t="inlineStr"/>
+      <c r="Q1262" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Militanter Mummenschanz vs. Kenny Omega &amp; Kota Ibushi</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr"/>
+      <c r="G1263" t="inlineStr"/>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>Masahiro Chono, Randy Orton, Kenny Omega, Kota Ibushi</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>Kenny Omega, Kota Ibushi</t>
+        </is>
+      </c>
+      <c r="J1263" t="inlineStr">
+        <is>
+          <t>Masahiro Chono, Randy Orton</t>
+        </is>
+      </c>
+      <c r="K1263" t="inlineStr"/>
+      <c r="L1263" t="inlineStr">
+        <is>
+          <t>Kota Ibushi beat Randy Orton in 46 Min 46 Sec with a Turnbuckle German Suplex</t>
+        </is>
+      </c>
+      <c r="M1263" t="inlineStr">
+        <is>
+          <t>46:46</t>
+        </is>
+      </c>
+      <c r="N1263" t="n">
+        <v>96</v>
+      </c>
+      <c r="O1263" t="inlineStr">
+        <is>
+          <t>★★★★¾</t>
+        </is>
+      </c>
+      <c r="P1263" t="inlineStr"/>
+      <c r="Q1263" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Steve Austin vs. Kota Ibushi</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr"/>
+      <c r="G1264" t="inlineStr"/>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>Steve Austin, Kota Ibushi</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>Kota Ibushi</t>
+        </is>
+      </c>
+      <c r="J1264" t="inlineStr">
+        <is>
+          <t>Steve Austin</t>
+        </is>
+      </c>
+      <c r="K1264" t="inlineStr"/>
+      <c r="L1264" t="inlineStr">
+        <is>
+          <t>Kota Ibushi beat Steve Austin in 12 Min 12 Sec with a Final Bomb</t>
+        </is>
+      </c>
+      <c r="M1264" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="N1264" t="n">
+        <v>78</v>
+      </c>
+      <c r="O1264" t="inlineStr">
+        <is>
+          <t>★★★½</t>
+        </is>
+      </c>
+      <c r="P1264" t="inlineStr"/>
+      <c r="Q1264" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada vs. Kota Ibushi</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr"/>
+      <c r="G1265" t="inlineStr"/>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada, Kota Ibushi</t>
+        </is>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada</t>
+        </is>
+      </c>
+      <c r="J1265" t="inlineStr">
+        <is>
+          <t>Kota Ibushi</t>
+        </is>
+      </c>
+      <c r="K1265" t="inlineStr"/>
+      <c r="L1265" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada beat Kota Ibushi in 32 Min 7 Sec with a Cobra Hold</t>
+        </is>
+      </c>
+      <c r="M1265" t="inlineStr">
+        <is>
+          <t>32:07</t>
+        </is>
+      </c>
+      <c r="N1265" t="n">
+        <v>104</v>
+      </c>
+      <c r="O1265" t="inlineStr">
+        <is>
+          <t>★★★★★¼</t>
+        </is>
+      </c>
+      <c r="P1265" t="inlineStr"/>
+      <c r="Q1265" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Kenny Omega vs. Kota Ibushi vs. Kazuchika Okada</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr"/>
+      <c r="G1266" t="inlineStr"/>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>Kenny Omega, Kota Ibushi, Kazuchika Okada</t>
+        </is>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada</t>
+        </is>
+      </c>
+      <c r="J1266" t="inlineStr">
+        <is>
+          <t>Kenny Omega, Kota Ibushi</t>
+        </is>
+      </c>
+      <c r="K1266" t="inlineStr"/>
+      <c r="L1266" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada won a triple threat match against Kenny Omega &amp; Kota Ibushi in  32:09</t>
+        </is>
+      </c>
+      <c r="M1266" t="inlineStr">
+        <is>
+          <t>32:09</t>
+        </is>
+      </c>
+      <c r="N1266" t="n">
+        <v>102</v>
+      </c>
+      <c r="O1266" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="P1266" t="inlineStr"/>
+      <c r="Q1266" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>S08E02_All In</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>1st Mariner Arena</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Baltimore, Maryland, USA</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Choke Slam World Championship: Kazuchika Okada vs. Yokozuna (c)</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr"/>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>Choke Slam World Championship</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada, Yokozuna</t>
+        </is>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada</t>
+        </is>
+      </c>
+      <c r="J1267" t="inlineStr">
+        <is>
+          <t>Yokozuna</t>
+        </is>
+      </c>
+      <c r="K1267" t="inlineStr"/>
+      <c r="L1267" t="inlineStr">
+        <is>
+          <t>Kazuchika Okada beat Yokozuna in 18 Min 8 Sec with a Rainmaker Lariat</t>
+        </is>
+      </c>
+      <c r="M1267" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="N1267" t="n">
+        <v>98</v>
+      </c>
+      <c r="O1267" t="inlineStr">
+        <is>
+          <t>★★★★¾</t>
+        </is>
+      </c>
+      <c r="P1267" t="inlineStr"/>
+      <c r="Q1267" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Choke_Slam_export.xlsx
+++ b/Choke_Slam_export.xlsx
@@ -85128,7 +85128,7 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1253" t="inlineStr">
@@ -85195,7 +85195,7 @@
       </c>
       <c r="B1254" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1254" t="inlineStr">
@@ -85266,7 +85266,7 @@
       </c>
       <c r="B1255" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1255" t="inlineStr">
@@ -85337,7 +85337,7 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1256" t="inlineStr">
@@ -85408,7 +85408,7 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1257" t="inlineStr">
@@ -85475,7 +85475,7 @@
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1258" t="inlineStr">
@@ -85546,7 +85546,7 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1259" t="inlineStr">
@@ -85620,7 +85620,7 @@
       </c>
       <c r="B1260" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1260" t="inlineStr">
@@ -85687,7 +85687,7 @@
       </c>
       <c r="B1261" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1261" t="inlineStr">
@@ -85754,7 +85754,7 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1262" t="inlineStr">
@@ -85821,7 +85821,7 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1263" t="inlineStr">
@@ -85888,7 +85888,7 @@
       </c>
       <c r="B1264" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1264" t="inlineStr">
@@ -85955,7 +85955,7 @@
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1265" t="inlineStr">
@@ -86022,7 +86022,7 @@
       </c>
       <c r="B1266" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1266" t="inlineStr">
@@ -86089,7 +86089,7 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>7/31/2026</t>
+          <t>9/14/2026</t>
         </is>
       </c>
       <c r="C1267" t="inlineStr">
